--- a/backend/src/main/resources/templates/temple-lead.xlsx
+++ b/backend/src/main/resources/templates/temple-lead.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="CI" sheetId="30" r:id="rId1"/>
@@ -161,6 +161,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>ACCOUNT NAME</t>
     </r>
     <r>
@@ -567,14 +573,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1469,20 +1475,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>305435</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>133985</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>503555</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>118745</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>664210</xdr:colOff>
+      <xdr:colOff>762000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>140335</xdr:rowOff>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2" descr="73c7f05700406c30116bf7709ac3f4b7"/>
+        <xdr:cNvPr id="2" name="图片 1" descr="73c7f05700406c30116bf7709ac3f4b7"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1495,8 +1501,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4095115" y="7338060"/>
-          <a:ext cx="1903095" cy="1652270"/>
+          <a:off x="3769995" y="6957060"/>
+          <a:ext cx="2326005" cy="2019935"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1835,7 +1841,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
@@ -2219,7 +2227,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:P30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -2720,7 +2730,7 @@
     <mergeCell ref="A17:K30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="82" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/backend/src/main/resources/templates/temple-lead.xlsx
+++ b/backend/src/main/resources/templates/temple-lead.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t xml:space="preserve">Issuer: {shipperCompany}
                                                                                  </t>
@@ -120,11 +120,10 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>FOB SHANGHAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHINA
-    </t>
+    <t>{tradeTerm} {port}</t>
+  </si>
+  <si>
+    <t>{currency}</t>
   </si>
   <si>
     <t>{.productName}</t>
@@ -146,9 +145,6 @@
   </si>
   <si>
     <t xml:space="preserve">      TOTAL:</t>
-  </si>
-  <si>
-    <t>{currency}</t>
   </si>
   <si>
     <t>{totalAmount}</t>
@@ -578,18 +574,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="16"/>
       <name val="NSimSun"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -785,7 +781,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -935,6 +931,26 @@
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1062,7 +1078,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1074,34 +1090,34 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1192,7 +1208,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1295,13 +1311,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1375,6 +1400,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1859,36 +1887,36 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="47"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" ht="47.45" customHeight="1" spans="1:7">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="47"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
     </row>
     <row r="3" ht="47.45" customHeight="1" spans="1:7">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
     </row>
     <row r="4" ht="47.45" customHeight="1" spans="1:7">
       <c r="A4" s="8" t="s">
@@ -1897,8 +1925,8 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="49"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="52"/>
       <c r="E4" s="9" t="s">
         <v>6</v>
       </c>
@@ -1906,7 +1934,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:7">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="53" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="12" t="s">
@@ -1919,7 +1947,7 @@
       <c r="G5" s="14"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:7">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="54" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="16"/>
@@ -1930,7 +1958,7 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:7">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="55" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="20"/>
@@ -1941,34 +1969,34 @@
       <c r="G7" s="22"/>
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:7">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="54" t="s">
+      <c r="C8" s="58"/>
+      <c r="D8" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="56" t="s">
+      <c r="E8" s="58"/>
+      <c r="F8" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="57"/>
+      <c r="G8" s="60"/>
     </row>
     <row r="9" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A9" s="58"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="60" t="s">
+      <c r="A9" s="61"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60" t="s">
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="61"/>
+      <c r="G9" s="65"/>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:7">
       <c r="A10" s="29" t="s">
@@ -1977,231 +2005,231 @@
       <c r="B10" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="E10" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="63" t="s">
+      <c r="F10" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="68" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" ht="21.95" customHeight="1" spans="1:7">
       <c r="A11" s="29"/>
       <c r="B11" s="30"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="64"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="68"/>
     </row>
     <row r="12" ht="21.95" customHeight="1" spans="1:7">
       <c r="A12" s="29"/>
       <c r="B12" s="30"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="64"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="68"/>
     </row>
     <row r="13" ht="21.95" customHeight="1" spans="1:7">
       <c r="A13" s="29"/>
       <c r="B13" s="30"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="64"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="68"/>
     </row>
     <row r="14" ht="21.95" customHeight="1" spans="1:7">
       <c r="A14" s="29"/>
       <c r="B14" s="30"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="64"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" spans="1:7">
       <c r="A15" s="29"/>
       <c r="B15" s="30"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="64"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="68"/>
     </row>
     <row r="16" ht="21.95" customHeight="1" spans="1:7">
       <c r="A16" s="29"/>
       <c r="B16" s="30"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="64"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="68"/>
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="65" t="s">
+      <c r="B17" s="69"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="67" t="s">
+    </row>
+    <row r="18" ht="21.95" customHeight="1" spans="1:7">
+      <c r="A18" s="72" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A18" s="68" t="s">
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="68"/>
+    </row>
+    <row r="19" ht="21.95" customHeight="1" spans="1:7">
+      <c r="A19" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="64"/>
-    </row>
-    <row r="19" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A19" s="68" t="s">
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="68"/>
+    </row>
+    <row r="20" ht="21.95" customHeight="1" spans="1:7">
+      <c r="A20" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="64"/>
-    </row>
-    <row r="20" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A20" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="42"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="45"/>
     </row>
     <row r="21" customHeight="1" spans="1:7">
-      <c r="A21" s="40"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="42"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="45"/>
     </row>
     <row r="22" customHeight="1" spans="1:7">
-      <c r="A22" s="40"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="42"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="45"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="40"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="42"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="45"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="40"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="42"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="45"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="40"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="42"/>
+      <c r="A25" s="43"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="45"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="40"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="42"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="45"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="40"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="42"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="45"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="40"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="42"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="45"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="40"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="42"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="45"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="40"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="42"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="45"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="40"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="42"/>
+      <c r="A31" s="43"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="45"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="43"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="45"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2251,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -2305,7 +2333,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -2315,7 +2343,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>8</v>
@@ -2365,23 +2393,23 @@
         <v>11</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I8" s="28"/>
       <c r="J8" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K8" s="28"/>
     </row>
@@ -2396,28 +2424,28 @@
         <v>19</v>
       </c>
       <c r="D9" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="F9" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="G9" t="s">
         <v>39</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="I9" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="32" t="s">
+      <c r="K9" s="33" t="s">
         <v>42</v>
-      </c>
-      <c r="K9" s="33" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
@@ -2475,245 +2503,245 @@
     <row r="14" ht="21.95" customHeight="1" spans="1:16">
       <c r="A14" s="29"/>
       <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="36"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="36"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
       <c r="D15" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="F15" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="G15" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="H15" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="I15" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" s="32" t="s">
+      <c r="K15" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="33" t="s">
+    </row>
+    <row r="16" ht="21.95" customHeight="1" spans="1:16">
+      <c r="A16" s="40" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A16" s="37" t="s">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="42"/>
+    </row>
+    <row r="17" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
-    </row>
-    <row r="17" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A17" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="42"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="45"/>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A18" s="40"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="42"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="45"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A19" s="40"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="42"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="45"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A20" s="40"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="42"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="45"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="40"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="42"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="45"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="40"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="42"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="45"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="40"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="45"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="40"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="42"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="45"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="40"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="42"/>
+      <c r="A25" s="43"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="45"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="40"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="42"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="45"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="40"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="42"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="40"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="42"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="45"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="40"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="42"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="45"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="45"/>
+      <c r="A30" s="46"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/backend/src/main/resources/templates/temple-lead.xlsx
+++ b/backend/src/main/resources/templates/temple-lead.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\lead-declaration-system\backend\src\main\resources\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="CI" sheetId="30" r:id="rId1"/>
@@ -325,12 +330,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
   </numFmts>
   <fonts count="36">
     <font>
@@ -568,16 +574,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="16"/>
       <name val="NSimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1208,7 +1214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1306,6 +1312,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1887,36 +1896,36 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="51"/>
     </row>
     <row r="2" ht="47.45" customHeight="1" spans="1:7">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51"/>
     </row>
     <row r="3" ht="47.45" customHeight="1" spans="1:7">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
     </row>
     <row r="4" ht="47.45" customHeight="1" spans="1:7">
       <c r="A4" s="8" t="s">
@@ -1925,8 +1934,8 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="9" t="s">
         <v>6</v>
       </c>
@@ -1934,7 +1943,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:7">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="54" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="12" t="s">
@@ -1947,7 +1956,7 @@
       <c r="G5" s="14"/>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:7">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="55" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="16"/>
@@ -1958,7 +1967,7 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:7">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="56" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="20"/>
@@ -1969,34 +1978,34 @@
       <c r="G7" s="22"/>
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:7">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="57" t="s">
+      <c r="C8" s="59"/>
+      <c r="D8" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="59" t="s">
+      <c r="E8" s="59"/>
+      <c r="F8" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="60"/>
+      <c r="G8" s="61"/>
     </row>
     <row r="9" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A9" s="61"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="63" t="s">
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="64" t="s">
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="65"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:7">
       <c r="A10" s="29" t="s">
@@ -2005,231 +2014,231 @@
       <c r="B10" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="66" t="s">
+      <c r="E10" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="67" t="s">
+      <c r="F10" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="69" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" ht="21.95" customHeight="1" spans="1:7">
       <c r="A11" s="29"/>
       <c r="B11" s="30"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="68"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="69"/>
     </row>
     <row r="12" ht="21.95" customHeight="1" spans="1:7">
       <c r="A12" s="29"/>
       <c r="B12" s="30"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="68"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="69"/>
     </row>
     <row r="13" ht="21.95" customHeight="1" spans="1:7">
       <c r="A13" s="29"/>
       <c r="B13" s="30"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="68"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="69"/>
     </row>
     <row r="14" ht="21.95" customHeight="1" spans="1:7">
       <c r="A14" s="29"/>
       <c r="B14" s="30"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="68"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="69"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" spans="1:7">
       <c r="A15" s="29"/>
       <c r="B15" s="30"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="68"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="69"/>
     </row>
     <row r="16" ht="21.95" customHeight="1" spans="1:7">
       <c r="A16" s="29"/>
       <c r="B16" s="30"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="68"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="69"/>
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="69" t="s">
+      <c r="B17" s="70"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="71" t="s">
+      <c r="G17" s="72" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A18" s="72" t="s">
+      <c r="A18" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="68"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="69"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="68"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="69"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:7">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="45"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
     </row>
     <row r="21" customHeight="1" spans="1:7">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="45"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="46"/>
     </row>
     <row r="22" customHeight="1" spans="1:7">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="45"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="46"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="45"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="46"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="43"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="45"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="46"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="45"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="43"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="45"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="43"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="45"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="46"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="45"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="46"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="45"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="46"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="45"/>
+      <c r="A30" s="44"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="46"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="43"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="45"/>
+      <c r="A31" s="44"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="46"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="46"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="48"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2441,10 +2450,10 @@
       <c r="I9" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="33" t="s">
+      <c r="K9" s="34" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2459,7 +2468,7 @@
       <c r="H10" s="32"/>
       <c r="I10" s="31"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="33"/>
+      <c r="K10" s="34"/>
     </row>
     <row r="11" ht="21.95" customHeight="1" spans="1:16">
       <c r="A11" s="29"/>
@@ -2472,7 +2481,7 @@
       <c r="H11" s="32"/>
       <c r="I11" s="31"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="33"/>
+      <c r="K11" s="34"/>
     </row>
     <row r="12" ht="21.95" customHeight="1" spans="1:16">
       <c r="A12" s="29"/>
@@ -2485,7 +2494,7 @@
       <c r="H12" s="32"/>
       <c r="I12" s="31"/>
       <c r="J12" s="32"/>
-      <c r="K12" s="33"/>
+      <c r="K12" s="34"/>
     </row>
     <row r="13" ht="21.95" customHeight="1" spans="1:16">
       <c r="A13" s="29"/>
@@ -2498,27 +2507,27 @@
       <c r="H13" s="32"/>
       <c r="I13" s="31"/>
       <c r="J13" s="32"/>
-      <c r="K13" s="33"/>
+      <c r="K13" s="34"/>
     </row>
     <row r="14" ht="21.95" customHeight="1" spans="1:16">
       <c r="A14" s="29"/>
       <c r="B14" s="30"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="30" t="s">
         <v>43</v>
       </c>
@@ -2537,211 +2546,211 @@
       <c r="I15" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="J15" s="32" t="s">
+      <c r="J15" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="33" t="s">
+      <c r="K15" s="34" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="16" ht="21.95" customHeight="1" spans="1:16">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="42"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="43"/>
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="45"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="46"/>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="45"/>
+      <c r="A18" s="44"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="46"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A19" s="43"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="45"/>
+      <c r="A19" s="44"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="46"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="45"/>
+      <c r="A20" s="44"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="46"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="45"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="46"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="45"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="46"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="45"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="46"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="43"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="45"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="46"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="45"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="46"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="43"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="45"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="46"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="43"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="45"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="46"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="45"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="46"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="45"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="46"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="46"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="48"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="11">
